--- a/datasets/gold/gold_ps_ce002.xlsx
+++ b/datasets/gold/gold_ps_ce002.xlsx
@@ -12378,15 +12378,15 @@
     <cfRule type="duplicateValues" dxfId="77" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E485:E488">
-    <cfRule type="duplicateValues" dxfId="76" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="100"/>
     <cfRule type="duplicateValues" dxfId="72" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E489:E1220">
     <cfRule type="duplicateValues" dxfId="67" priority="62"/>
@@ -12396,72 +12396,72 @@
     <cfRule type="duplicateValues" dxfId="65" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1110:E1111 E489:E689 E691:E781 E895:E1108">
-    <cfRule type="duplicateValues" dxfId="64" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1110:E1111 E489:E689 E691:E1108">
-    <cfRule type="duplicateValues" dxfId="60" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1110:E1111 E530:E689 E691:E781 E895:E1108">
     <cfRule type="duplicateValues" dxfId="57" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1110:E1111">
-    <cfRule type="duplicateValues" dxfId="56" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1112:E1220 E690">
-    <cfRule type="duplicateValues" dxfId="49" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1221:E1535">
-    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1221:E1586">
     <cfRule type="duplicateValues" dxfId="32" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1221:E1642">
-    <cfRule type="duplicateValues" dxfId="31" priority="1838"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1840"/>
     <cfRule type="duplicateValues" dxfId="30" priority="1839"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="1840"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1838"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1536:E1583">
     <cfRule type="duplicateValues" dxfId="28" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1536:E1586">
-    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1585:E1586">
     <cfRule type="duplicateValues" dxfId="16" priority="21"/>
@@ -12470,18 +12470,18 @@
     <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1643:E1048576 E1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1749"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1750"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1751"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1752"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1753"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1754"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1755"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1756"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1757"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1758"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1759"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1760"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1754"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1753"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1755"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1756"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1757"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1758"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1759"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1760"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1752"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1751"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1749"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1750"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1643:E1048576 E1:E51">
     <cfRule type="duplicateValues" dxfId="2" priority="1745"/>
